--- a/branches/dev/StructureDefinition-mii-ext-seltene-syndrome-category.xlsx
+++ b/branches/dev/StructureDefinition-mii-ext-seltene-syndrome-category.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T10:39:42+00:00</t>
+    <t>2026-07-23T11:20:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/StructureDefinition-mii-ext-seltene-syndrome-category.xlsx
+++ b/branches/dev/StructureDefinition-mii-ext-seltene-syndrome-category.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T11:20:28+00:00</t>
+    <t>2026-07-23T15:55:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/StructureDefinition-mii-ext-seltene-syndrome-category.xlsx
+++ b/branches/dev/StructureDefinition-mii-ext-seltene-syndrome-category.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T15:55:45+00:00</t>
+    <t>2026-07-24T06:29:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
